--- a/data/trans_dic/P16A_n_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,29</t>
+          <t>2,19; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,21</t>
+          <t>3,15; 6,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,74</t>
+          <t>3,6; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,28</t>
+          <t>10,16; 15,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,19</t>
+          <t>3,74; 6,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,58</t>
+          <t>8,95; 12,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,99</t>
+          <t>8,14; 12,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,77; 27,81</t>
+          <t>22,51; 27,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,98</t>
+          <t>3,33; 4,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 9,18</t>
+          <t>6,88; 9,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,12</t>
+          <t>6,55; 9,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 21,88</t>
+          <t>18,33; 21,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,27</t>
+          <t>0,37; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,13</t>
+          <t>0,32; 1,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,17</t>
+          <t>0,41; 1,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,19</t>
+          <t>2,32; 4,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,0</t>
+          <t>0,89; 2,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,98</t>
+          <t>0,92; 2,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,05</t>
+          <t>1,65; 3,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,13</t>
+          <t>3,71; 6,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,43</t>
+          <t>0,72; 1,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,43</t>
+          <t>0,72; 1,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,93</t>
+          <t>1,13; 1,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,91</t>
+          <t>3,4; 4,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,21</t>
+          <t>0,38; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,83</t>
+          <t>0,17; 1,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,54</t>
+          <t>1,48; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,8</t>
+          <t>0,9; 3,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,92</t>
+          <t>0,69; 3,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,11</t>
+          <t>2,71; 5,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,18</t>
+          <t>0,2; 1,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,05</t>
+          <t>0,81; 2,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,97</t>
+          <t>0,48; 1,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,85</t>
+          <t>2,26; 3,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,97</t>
+          <t>1,12; 1,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,46</t>
+          <t>1,39; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,13</t>
+          <t>1,25; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,27</t>
+          <t>3,52; 5,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,2</t>
+          <t>2,11; 3,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,72</t>
+          <t>4,32; 5,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,0</t>
+          <t>3,61; 5,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,01</t>
+          <t>7,31; 9,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,42</t>
+          <t>1,71; 2,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,92</t>
+          <t>3,01; 3,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,42</t>
+          <t>2,6; 3,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,5</t>
+          <t>5,89; 7,53</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22617; 44269</t>
+          <t>22619; 45430</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31317; 60518</t>
+          <t>30725; 59917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28066; 50815</t>
+          <t>27166; 50778</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53087; 78662</t>
+          <t>52336; 78838</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50019; 81355</t>
+          <t>49150; 80503</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>121638; 168297</t>
+          <t>119668; 169415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79353; 119309</t>
+          <t>80924; 121326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>172020; 210101</t>
+          <t>170060; 210100</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80057; 116795</t>
+          <t>78184; 114873</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158602; 212328</t>
+          <t>159087; 212951</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112950; 159425</t>
+          <t>114539; 159163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>231787; 277995</t>
+          <t>232827; 278127</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6223; 21531</t>
+          <t>6237; 20301</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6837; 22272</t>
+          <t>6295; 21954</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8665; 24281</t>
+          <t>8578; 26022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51872; 95865</t>
+          <t>53118; 95933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13021; 31708</t>
+          <t>14121; 33658</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16197; 34880</t>
+          <t>16144; 36346</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33367; 60626</t>
+          <t>32750; 62073</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85149; 137242</t>
+          <t>82957; 136273</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23262; 47075</t>
+          <t>23580; 46491</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26900; 53112</t>
+          <t>26744; 52056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45476; 78612</t>
+          <t>45834; 79784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>152748; 222242</t>
+          <t>153953; 221302</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1779; 11440</t>
+          <t>1760; 10135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1852; 15425</t>
+          <t>1846; 16309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>927; 10017</t>
+          <t>941; 10697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9021; 22908</t>
+          <t>9601; 23401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 5616</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4170; 17411</t>
+          <t>4121; 16535</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3221; 16042</t>
+          <t>3769; 16872</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18052; 33745</t>
+          <t>17929; 33301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1983; 12137</t>
+          <t>2092; 12350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7482; 28682</t>
+          <t>7619; 26765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5392; 21571</t>
+          <t>5307; 21138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29763; 50264</t>
+          <t>29547; 50280</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36592; 64528</t>
+          <t>36732; 62924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47229; 84021</t>
+          <t>47429; 81442</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41885; 71831</t>
+          <t>42226; 71578</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120105; 181987</t>
+          <t>121338; 181016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69379; 108246</t>
+          <t>71158; 107516</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>151835; 203366</t>
+          <t>153399; 204901</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127532; 176603</t>
+          <t>127366; 178612</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>269676; 365618</t>
+          <t>267218; 361935</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113981; 161115</t>
+          <t>113739; 160060</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>207937; 273502</t>
+          <t>209936; 271588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>178032; 236488</t>
+          <t>179757; 236530</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>421596; 533233</t>
+          <t>418555; 535229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,4</t>
+          <t>2,17; 4,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,15</t>
+          <t>3,2; 6,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,73</t>
+          <t>3,76; 6,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,31</t>
+          <t>10,05; 14,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,12</t>
+          <t>3,82; 6,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,66</t>
+          <t>9,07; 12,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,2</t>
+          <t>7,88; 12,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 27,81</t>
+          <t>22,43; 26,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,89</t>
+          <t>3,33; 4,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,21</t>
+          <t>6,95; 9,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,1</t>
+          <t>6,62; 9,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,89</t>
+          <t>17,53; 21,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,2</t>
+          <t>0,36; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,12</t>
+          <t>0,33; 1,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,25</t>
+          <t>0,37; 1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,19</t>
+          <t>2,98; 4,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,12</t>
+          <t>0,85; 2,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,07</t>
+          <t>0,92; 2,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,12</t>
+          <t>1,67; 3,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,09</t>
+          <t>5,12; 6,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,42</t>
+          <t>0,7; 1,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,4</t>
+          <t>0,7; 1,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,96</t>
+          <t>1,12; 1,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,89</t>
+          <t>4,22; 5,22</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,84</t>
+          <t>0,34; 1,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,39</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,96</t>
+          <t>0,17; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,62</t>
+          <t>1,54; 3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,61</t>
+          <t>0,87; 3,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,07</t>
+          <t>0,57; 2,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,04</t>
+          <t>2,81; 5,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,2</t>
+          <t>0,21; 1,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,85</t>
+          <t>0,83; 2,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,93</t>
+          <t>0,52; 1,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,85</t>
+          <t>2,43; 3,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,92</t>
+          <t>1,12; 2,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,38</t>
+          <t>1,37; 2,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,12</t>
+          <t>1,27; 2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,24</t>
+          <t>4,15; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,18</t>
+          <t>2,1; 3,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,77</t>
+          <t>4,28; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,06</t>
+          <t>3,65; 5,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 9,91</t>
+          <t>8,81; 10,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,4</t>
+          <t>1,72; 2,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,89</t>
+          <t>2,96; 3,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,42</t>
+          <t>2,64; 3,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,53</t>
+          <t>6,71; 7,74</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>69774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>189408</t>
+          <t>201429</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>271203</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22619; 45430</t>
+          <t>22362; 45530</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30725; 59917</t>
+          <t>31150; 59704</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27166; 50778</t>
+          <t>28380; 49996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52336; 78838</t>
+          <t>58131; 84058</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>49150; 80503</t>
+          <t>50282; 81602</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>119668; 169415</t>
+          <t>121342; 168597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80924; 121326</t>
+          <t>78331; 120476</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>170060; 210100</t>
+          <t>184376; 220153</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78184; 114873</t>
+          <t>78225; 117015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159087; 212951</t>
+          <t>160796; 217350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114539; 159163</t>
+          <t>115839; 161572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>232827; 278127</t>
+          <t>245550; 295610</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76488</t>
+          <t>80215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>115277</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>191765</t>
+          <t>206566</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6237; 20301</t>
+          <t>6135; 19973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6295; 21954</t>
+          <t>6519; 23519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8578; 26022</t>
+          <t>7653; 25179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53118; 95933</t>
+          <t>66452; 97719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14121; 33658</t>
+          <t>13458; 32022</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16144; 36346</t>
+          <t>16257; 37571</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32750; 62073</t>
+          <t>33137; 60378</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82957; 136273</t>
+          <t>111162; 144415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23580; 46491</t>
+          <t>23009; 45539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26744; 52056</t>
+          <t>26136; 49813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45834; 79784</t>
+          <t>45501; 77364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153953; 221302</t>
+          <t>185737; 229987</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>28164</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>45590</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1760; 10135</t>
+          <t>1890; 10555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1846; 16309</t>
+          <t>1855; 16721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>941; 10697</t>
+          <t>924; 9256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9601; 23401</t>
+          <t>10943; 25686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5616</t>
+          <t>0; 5601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4121; 16535</t>
+          <t>4000; 17146</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3769; 16872</t>
+          <t>3118; 15779</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17929; 33301</t>
+          <t>20664; 37958</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2092; 12350</t>
+          <t>2127; 11979</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7619; 26765</t>
+          <t>7763; 27136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5307; 21138</t>
+          <t>5717; 21221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29547; 50280</t>
+          <t>35169; 57737</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>329215</t>
+          <t>355945</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>485752</t>
+          <t>523360</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36732; 62924</t>
+          <t>36699; 66042</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47429; 81442</t>
+          <t>46683; 81837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42226; 71578</t>
+          <t>43022; 72037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121338; 181016</t>
+          <t>146058; 192536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71158; 107516</t>
+          <t>71073; 109134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>153399; 204901</t>
+          <t>152226; 204426</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127366; 178612</t>
+          <t>128988; 181362</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>267218; 361935</t>
+          <t>328317; 382762</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113739; 160060</t>
+          <t>114323; 159065</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>209936; 271588</t>
+          <t>206524; 270897</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>179757; 236530</t>
+          <t>182396; 239961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>418555; 535229</t>
+          <t>486456; 561393</t>
         </is>
       </c>
     </row>
